--- a/KatalonData/RADTestData/ChangePaymentMethodCorp.xlsx
+++ b/KatalonData/RADTestData/ChangePaymentMethodCorp.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
@@ -26,7 +26,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="389">
   <si>
     <t>Result</t>
   </si>
@@ -717,12 +717,508 @@
   </si>
   <si>
     <t>Mon Aug 03 15:25:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:11:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:12:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:13:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:14:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:15:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:17:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:18:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:19:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:20:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:21:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:22:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:23:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:24:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:25:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:27:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:28:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:29:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:31:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:33:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:34:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:35:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:37:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:38:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:39:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:40:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:41:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:42:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:43:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:44:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:45:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:47:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:48:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:49:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:49:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:50:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:51:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:52:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:53:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:54:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:55:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:56:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:57:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:58:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:59:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:00:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:04:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:05:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:07:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:08:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:09:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:11:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:12:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:13:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:14:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:16:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:17:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:18:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:19:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:21:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:23:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:24:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:25:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:26:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:27:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:28:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:29:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:30:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:31:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:32:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:33:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:34:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:35:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:36:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:37:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:37:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:38:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:39:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:41:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:42:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:43:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:44:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:44:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:45:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:46:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:47:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:48:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:49:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:50:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:51:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:52:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:53:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:54:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:55:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:56:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:56:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:57:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:58:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 03:59:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:01:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:02:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:03:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:04:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:05:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:05:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:06:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:07:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:08:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:09:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:11:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:12:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:13:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:14:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:15:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:16:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:17:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:18:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:20:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:21:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:23:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:25:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:26:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:27:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:28:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:29:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:30:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:31:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:33:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:34:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:35:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:36:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:36:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:37:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:38:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:39:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:41:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:42:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:43:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:44:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:45:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:46:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:47:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:48:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:49:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:50:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:51:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:52:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:52:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:53:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:55:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:56:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:57:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:58:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 04:59:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:01:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:01:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:03:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:04:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:05:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:06:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:07:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:08:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:09:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:10:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:11:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:12:50 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1095,17 +1591,17 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="18.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1145,7 +1641,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1174,7 +1670,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>171</v>
+        <v>225</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1203,7 +1699,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>172</v>
+        <v>226</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1235,7 +1731,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>173</v>
+        <v>227</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1267,7 +1763,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>174</v>
+        <v>228</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1299,7 +1795,7 @@
         <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>175</v>
+        <v>229</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1331,7 +1827,7 @@
         <v>114</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>176</v>
+        <v>230</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1364,16 +1860,16 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="43.33203125" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.59765625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="43.33203125" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1413,7 +1909,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>177</v>
+        <v>231</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1436,7 +1932,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>178</v>
+        <v>232</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1459,7 +1955,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>179</v>
+        <v>233</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1482,7 +1978,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>180</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1508,7 +2004,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>181</v>
+        <v>235</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1534,7 +2030,7 @@
         <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>182</v>
+        <v>236</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1557,7 +2053,7 @@
         <v>114</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>183</v>
+        <v>237</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1580,7 +2076,7 @@
         <v>114</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>184</v>
+        <v>238</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -1603,7 +2099,7 @@
         <v>114</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>185</v>
+        <v>239</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -1626,7 +2122,7 @@
         <v>114</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>186</v>
+        <v>240</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -1649,7 +2145,7 @@
         <v>114</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>187</v>
+        <v>241</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -1672,7 +2168,7 @@
         <v>114</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>188</v>
+        <v>242</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -1695,7 +2191,7 @@
         <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -1718,7 +2214,7 @@
         <v>114</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -1738,7 +2234,7 @@
         <v>114</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -1764,7 +2260,7 @@
         <v>114</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>192</v>
+        <v>246</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -1787,7 +2283,7 @@
         <v>114</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>193</v>
+        <v>247</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -1827,7 +2323,7 @@
         <v>114</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>194</v>
+        <v>248</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -1872,15 +2368,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -1917,7 +2413,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>195</v>
+        <v>249</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1943,7 +2439,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>196</v>
+        <v>250</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1966,7 +2462,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>197</v>
+        <v>251</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1992,7 +2488,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>198</v>
+        <v>252</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2018,7 +2514,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>199</v>
+        <v>253</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2044,7 +2540,7 @@
         <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>200</v>
+        <v>254</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2079,17 +2575,17 @@
   <dimension ref="A1:M64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="41.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="10" width="19.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="19.796875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.19921875" style="1" collapsed="1"/>
-    <col min="13" max="13" width="43.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="41.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="10" customWidth="true" style="1" width="19.796875" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="1" width="19.796875"/>
+    <col min="12" max="12" style="1" width="9.19921875" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="43.19921875" collapsed="true"/>
+    <col min="14" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
@@ -2138,7 +2634,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>116</v>
+        <v>315</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -2161,7 +2657,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>117</v>
+        <v>316</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -2187,7 +2683,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>118</v>
+        <v>317</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2213,7 +2709,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>119</v>
+        <v>318</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2239,7 +2735,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>120</v>
+        <v>319</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2265,7 +2761,7 @@
         <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>121</v>
+        <v>320</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2288,7 +2784,7 @@
         <v>114</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>122</v>
+        <v>321</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -2314,7 +2810,7 @@
         <v>114</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>123</v>
+        <v>322</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -2340,7 +2836,7 @@
         <v>114</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>124</v>
+        <v>323</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -2366,7 +2862,7 @@
         <v>114</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>125</v>
+        <v>324</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -2392,7 +2888,7 @@
         <v>114</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>126</v>
+        <v>325</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -2415,7 +2911,7 @@
         <v>114</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>127</v>
+        <v>326</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -2441,7 +2937,7 @@
         <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>128</v>
+        <v>327</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -2467,7 +2963,7 @@
         <v>114</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>129</v>
+        <v>328</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -2493,7 +2989,7 @@
         <v>114</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>130</v>
+        <v>329</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -2519,7 +3015,7 @@
         <v>114</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>131</v>
+        <v>330</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -2548,7 +3044,7 @@
         <v>114</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>132</v>
+        <v>331</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -2577,7 +3073,7 @@
         <v>114</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>133</v>
+        <v>332</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>29</v>
@@ -2606,7 +3102,7 @@
         <v>114</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>134</v>
+        <v>333</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -2629,7 +3125,7 @@
         <v>114</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>135</v>
+        <v>334</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>29</v>
@@ -2658,7 +3154,7 @@
         <v>114</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>136</v>
+        <v>335</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>29</v>
@@ -2687,7 +3183,7 @@
         <v>114</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>137</v>
+        <v>336</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
@@ -2713,7 +3209,7 @@
         <v>114</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>138</v>
+        <v>337</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
@@ -2742,7 +3238,7 @@
         <v>114</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>139</v>
+        <v>338</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
@@ -2774,7 +3270,7 @@
         <v>114</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>140</v>
+        <v>339</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
@@ -2803,7 +3299,7 @@
         <v>114</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>141</v>
+        <v>340</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>29</v>
@@ -2832,7 +3328,7 @@
         <v>114</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>142</v>
+        <v>341</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>29</v>
@@ -2864,7 +3360,7 @@
         <v>114</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>143</v>
+        <v>342</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>29</v>
@@ -2893,7 +3389,7 @@
         <v>114</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>144</v>
+        <v>343</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>29</v>
@@ -2922,7 +3418,7 @@
         <v>114</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>145</v>
+        <v>344</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>29</v>
@@ -2951,7 +3447,7 @@
         <v>114</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>146</v>
+        <v>345</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
@@ -2974,7 +3470,7 @@
         <v>114</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>147</v>
+        <v>346</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>29</v>
@@ -3003,7 +3499,7 @@
         <v>114</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>148</v>
+        <v>347</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>29</v>
@@ -3032,7 +3528,7 @@
         <v>114</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>149</v>
+        <v>348</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>29</v>
@@ -3058,7 +3554,7 @@
         <v>114</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>150</v>
+        <v>349</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
@@ -3087,7 +3583,7 @@
         <v>114</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>151</v>
+        <v>350</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>29</v>
@@ -3119,7 +3615,7 @@
         <v>114</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>152</v>
+        <v>351</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>29</v>
@@ -3148,7 +3644,7 @@
         <v>114</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>153</v>
+        <v>352</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>29</v>
@@ -3177,7 +3673,7 @@
         <v>114</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>154</v>
+        <v>353</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>29</v>
@@ -3209,7 +3705,7 @@
         <v>114</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>155</v>
+        <v>354</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
@@ -3238,7 +3734,7 @@
         <v>114</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>156</v>
+        <v>355</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
@@ -3267,7 +3763,7 @@
         <v>114</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>157</v>
+        <v>356</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
@@ -3296,7 +3792,7 @@
         <v>114</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>158</v>
+        <v>357</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>29</v>
@@ -3319,7 +3815,7 @@
         <v>114</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>201</v>
+        <v>358</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>29</v>
@@ -3348,7 +3844,7 @@
         <v>114</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>159</v>
+        <v>359</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>29</v>
@@ -3377,7 +3873,7 @@
         <v>114</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>160</v>
+        <v>360</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>29</v>
@@ -3403,7 +3899,7 @@
         <v>114</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>161</v>
+        <v>361</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>29</v>
@@ -3432,7 +3928,7 @@
         <v>114</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>162</v>
+        <v>362</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>29</v>
@@ -3464,7 +3960,7 @@
         <v>114</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>29</v>
@@ -3493,7 +3989,7 @@
         <v>114</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>29</v>
@@ -3522,7 +4018,7 @@
         <v>114</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>29</v>
@@ -3554,7 +4050,7 @@
         <v>114</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>166</v>
+        <v>366</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>29</v>
@@ -3574,10 +4070,10 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>217</v>
+        <v>114</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>218</v>
+        <v>367</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>29</v>
@@ -3623,7 +4119,7 @@
         <v>114</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>202</v>
+        <v>368</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>29</v>
@@ -3646,7 +4142,7 @@
         <v>114</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>219</v>
+        <v>369</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>29</v>
@@ -3692,7 +4188,7 @@
         <v>114</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>167</v>
+        <v>370</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>29</v>
@@ -3715,7 +4211,7 @@
         <v>114</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>220</v>
+        <v>371</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>29</v>
@@ -3761,7 +4257,7 @@
         <v>114</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>203</v>
+        <v>372</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>29</v>
@@ -3787,7 +4283,7 @@
         <v>114</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>204</v>
+        <v>373</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>29</v>
@@ -3813,7 +4309,7 @@
         <v>114</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>205</v>
+        <v>374</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>29</v>
@@ -3849,14 +4345,14 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="23.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="23.46484375" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -3890,7 +4386,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>207</v>
+        <v>376</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -3913,7 +4409,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>208</v>
+        <v>377</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -3936,7 +4432,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>209</v>
+        <v>378</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -3959,7 +4455,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>210</v>
+        <v>379</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -3982,7 +4478,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>211</v>
+        <v>380</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4005,7 +4501,7 @@
         <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>221</v>
+        <v>381</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -4025,7 +4521,7 @@
         <v>114</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>222</v>
+        <v>382</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -4044,8 +4540,8 @@
       <c r="A9" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B9" t="s">
-        <v>223</v>
+      <c r="B9" t="s" s="1">
+        <v>383</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -4070,14 +4566,14 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
+    <col min="8" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -4108,7 +4604,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>212</v>
+        <v>384</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4131,7 +4627,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>213</v>
+        <v>385</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -4154,7 +4650,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>214</v>
+        <v>386</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -4177,7 +4673,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>215</v>
+        <v>387</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -4200,7 +4696,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>216</v>
+        <v>388</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4228,12 +4724,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -4261,7 +4757,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>206</v>
+        <v>375</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
